--- a/experiment/RQ2_relationship.xlsx
+++ b/experiment/RQ2_relationship.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\research\7-Agent-Empirical\RQ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\research\7-MATester\agents\MATester\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CED6FF8-8340-43EC-9F39-35DB6AA914E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEDF000-C981-4020-96A5-DDFD9EBA27AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="location &amp; symptom (sum)" sheetId="13" r:id="rId1"/>
@@ -891,8 +891,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="19">
-        <f>SUM('location &amp; sympton (survey)'!L3,'location &amp; sympton (github)'!L3,'location &amp; sympton (conference)'!L3)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M3" s="25">
         <f>SUM('location &amp; sympton (survey)'!M3,'location &amp; sympton (github)'!M3,'location &amp; sympton (conference)'!M3)</f>
@@ -916,7 +915,7 @@
       </c>
       <c r="R3" s="3">
         <f>SUM(B3:Q3)</f>
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -1660,8 +1659,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="19">
-        <f>SUM('location &amp; root cause (survey)'!L6,'location &amp; root cause (github)'!L6,'location &amp; root cause (confere)'!L6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" s="26">
         <f>SUM('location &amp; root cause (survey)'!M6,'location &amp; root cause (github)'!M6,'location &amp; root cause (confere)'!M6)</f>
@@ -1685,7 +1683,7 @@
       </c>
       <c r="R6" s="5">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -3587,7 +3585,9 @@
         <v>3</v>
       </c>
       <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
+      <c r="L3" s="2">
+        <v>1</v>
+      </c>
       <c r="M3" s="3"/>
       <c r="N3" s="1"/>
       <c r="O3" s="19">
@@ -3597,7 +3597,7 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="5">
         <f>SUM(B3:Q3)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -3951,7 +3951,9 @@
         <v>3</v>
       </c>
       <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
+      <c r="L6" s="2">
+        <v>1</v>
+      </c>
       <c r="M6" s="3"/>
       <c r="N6" s="1"/>
       <c r="O6" s="13">
@@ -3963,7 +3965,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="5">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
